--- a/thailand/budget_layer_all_years.xlsx
+++ b/thailand/budget_layer_all_years.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J302"/>
+  <dimension ref="A1:M302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,21 @@
           <t>source_file</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>programme_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>class_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>strategy_name_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,6 +525,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,6 +577,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,6 +637,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,6 +697,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,6 +757,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -760,6 +817,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,6 +877,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -860,6 +937,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -910,6 +997,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -960,6 +1057,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1010,6 +1117,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1060,6 +1177,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1110,6 +1237,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1160,6 +1297,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1210,6 +1357,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1250,6 +1407,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1300,6 +1459,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1350,6 +1519,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1400,6 +1579,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1450,6 +1639,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1500,6 +1699,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1550,6 +1759,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1600,6 +1819,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1650,6 +1879,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1700,6 +1939,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1750,6 +1999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1800,6 +2059,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1850,6 +2119,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1900,6 +2179,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1950,6 +2239,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2000,6 +2299,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2040,6 +2349,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2090,6 +2401,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2140,6 +2461,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2190,6 +2521,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2240,6 +2581,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2290,6 +2641,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2340,6 +2701,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2390,6 +2761,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2440,6 +2821,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2480,6 +2871,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2530,6 +2923,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2580,6 +2983,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2630,6 +3043,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2680,6 +3103,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2730,6 +3163,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2780,6 +3223,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2830,6 +3283,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2880,6 +3343,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2930,6 +3403,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2980,6 +3463,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3030,6 +3523,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3070,6 +3573,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3120,6 +3625,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3170,6 +3685,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3220,6 +3745,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3270,6 +3805,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3320,6 +3865,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3370,6 +3925,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3420,6 +3985,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3470,6 +4045,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3520,6 +4105,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3560,6 +4155,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3610,6 +4207,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3660,6 +4267,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3710,6 +4327,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3760,6 +4387,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3810,6 +4447,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3860,6 +4507,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3910,6 +4567,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3950,6 +4617,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4000,6 +4669,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4050,6 +4729,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2023.xlsx</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4090,6 +4779,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4140,6 +4831,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4190,6 +4891,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4240,6 +4951,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4290,6 +5011,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4340,6 +5071,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4390,6 +5131,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4440,6 +5191,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4490,6 +5251,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4540,6 +5311,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4590,6 +5371,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4640,6 +5431,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4690,6 +5491,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4740,6 +5551,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4780,6 +5601,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4830,6 +5653,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4880,6 +5713,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4930,6 +5773,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4980,6 +5833,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5030,6 +5893,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5080,6 +5953,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5130,6 +6013,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5180,6 +6073,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5230,6 +6133,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5280,6 +6193,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5330,6 +6253,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5380,6 +6313,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5430,6 +6373,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5480,6 +6433,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5530,6 +6493,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5580,6 +6553,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5620,6 +6603,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5670,6 +6655,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5720,6 +6715,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5770,6 +6775,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5820,6 +6835,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5870,6 +6895,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5920,6 +6955,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5970,6 +7015,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6020,6 +7075,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6060,6 +7125,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6110,6 +7177,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6160,6 +7237,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6210,6 +7297,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6260,6 +7357,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6310,6 +7417,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6360,6 +7477,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6410,6 +7537,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6460,6 +7597,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6510,6 +7657,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6560,6 +7717,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6610,6 +7777,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6650,6 +7827,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6700,6 +7879,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6750,6 +7939,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6800,6 +7999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6850,6 +8059,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6900,6 +8119,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6950,6 +8179,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7000,6 +8239,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7050,6 +8299,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7100,6 +8359,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7150,6 +8419,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7190,6 +8469,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7240,6 +8521,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7290,6 +8581,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7340,6 +8641,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7390,6 +8701,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7440,6 +8761,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7490,6 +8821,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7540,6 +8881,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7580,6 +8931,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7630,6 +8983,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7680,6 +9043,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7730,6 +9103,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7770,6 +9153,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7820,6 +9205,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7870,6 +9265,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7920,6 +9325,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7970,6 +9385,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8020,6 +9445,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8070,6 +9505,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8120,6 +9565,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8170,6 +9625,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8220,6 +9685,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8270,6 +9745,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8320,6 +9805,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8370,6 +9865,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8420,6 +9925,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8460,6 +9975,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8510,6 +10027,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8560,6 +10087,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8610,6 +10147,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8660,6 +10207,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8710,6 +10267,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8760,6 +10327,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8810,6 +10387,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8860,6 +10447,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8910,6 +10507,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8960,6 +10567,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9010,6 +10627,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9060,6 +10687,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9110,6 +10747,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9160,6 +10807,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9210,6 +10867,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9260,6 +10927,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9310,6 +10987,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9350,6 +11037,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9400,6 +11089,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9450,6 +11149,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9500,6 +11209,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9550,6 +11269,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9600,6 +11329,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9650,6 +11389,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9700,6 +11449,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9750,6 +11509,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9790,6 +11559,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9840,6 +11611,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9890,6 +11671,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9940,6 +11731,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9990,6 +11791,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10040,6 +11851,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10090,6 +11911,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10140,6 +11971,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10190,6 +12031,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10240,6 +12091,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10290,6 +12151,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10340,6 +12211,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10390,6 +12271,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10430,6 +12321,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10480,6 +12373,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10530,6 +12433,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10580,6 +12493,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10630,6 +12553,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10680,6 +12613,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10730,6 +12673,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10780,6 +12733,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10830,6 +12793,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10880,6 +12853,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10930,6 +12913,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10970,6 +12963,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11020,6 +13015,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11070,6 +13075,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11120,6 +13135,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11170,6 +13195,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11220,6 +13255,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11270,6 +13315,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11320,6 +13375,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11360,6 +13425,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11410,6 +13477,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11460,6 +13537,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11500,6 +13587,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11550,6 +13639,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11600,6 +13699,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11650,6 +13759,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11700,6 +13819,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11750,6 +13879,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11800,6 +13939,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11850,6 +13999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11900,6 +14059,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11950,6 +14119,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12000,6 +14179,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12050,6 +14239,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12100,6 +14299,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12150,6 +14359,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12200,6 +14419,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12240,6 +14469,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12290,6 +14521,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12340,6 +14581,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12390,6 +14641,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12440,6 +14701,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12490,6 +14761,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12540,6 +14821,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12590,6 +14881,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12640,6 +14941,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12690,6 +15001,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12740,6 +15061,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12790,6 +15121,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12840,6 +15181,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12890,6 +15241,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12940,6 +15301,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12990,6 +15361,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13040,6 +15421,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13080,6 +15471,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13130,6 +15523,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13180,6 +15583,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13230,6 +15643,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13280,6 +15703,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13330,6 +15763,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13380,6 +15823,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13430,6 +15883,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13480,6 +15943,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13520,6 +15993,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13570,6 +16045,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13620,6 +16105,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13670,6 +16165,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13720,6 +16225,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13770,6 +16285,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13820,6 +16345,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13870,6 +16405,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13920,6 +16465,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13970,6 +16525,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14020,6 +16585,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14070,6 +16645,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14120,6 +16705,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14160,6 +16755,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14210,6 +16807,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14260,6 +16867,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14310,6 +16927,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14360,6 +16987,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14410,6 +17047,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14460,6 +17107,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14510,6 +17167,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14560,6 +17227,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14610,6 +17287,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14660,6 +17347,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14700,6 +17397,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14750,6 +17449,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14800,6 +17509,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14850,6 +17569,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14900,6 +17629,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14950,6 +17689,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15000,6 +17749,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15050,6 +17809,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15090,6 +17859,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15140,6 +17911,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15190,6 +17971,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15238,6 +18029,16 @@
       <c r="J302" t="inlineStr">
         <is>
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/thailand/thailand_budget_2026.xlsx</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>

--- a/thailand/budget_layer_all_years.xlsx
+++ b/thailand/budget_layer_all_years.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="budget_all_years" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs_wide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="national_total" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20536,7 +20537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20547,27 +20548,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>head_total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>strategy_total</t>
+          <t>programme_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>program_sum</t>
+          <t>gap_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nested_heads</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -20577,726 +20583,106 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>3185000</v>
       </c>
       <c r="C2" t="n">
-        <v>296003.6</v>
+        <v>3185000</v>
       </c>
       <c r="D2" t="n">
-        <v>296003.6</v>
-      </c>
-      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3185000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3480000</v>
       </c>
       <c r="C3" t="n">
-        <v>396125.5</v>
+        <v>3480000</v>
       </c>
       <c r="D3" t="n">
-        <v>396125.5000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-5.820766091346741e-11</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3480000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3752700</v>
       </c>
       <c r="C4" t="n">
-        <v>549514</v>
+        <v>3752700</v>
       </c>
       <c r="D4" t="n">
-        <v>549514</v>
-      </c>
-      <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3752700</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3780600</v>
       </c>
       <c r="C5" t="n">
-        <v>759861.3</v>
+        <v>3780600</v>
       </c>
       <c r="D5" t="n">
-        <v>759861.3</v>
-      </c>
-      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>122964.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>122964.9</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>658012.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>658012.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>402518</v>
-      </c>
-      <c r="D8" t="n">
-        <v>402518</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>386149.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>386149.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>392028.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>392028.6000000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>561167.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>561167.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>836382.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>836382.4999999999</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.164153218269348e-10</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>131020.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>131020.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>608210.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>608210.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>565041.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>565041.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>403868</v>
-      </c>
-      <c r="D16" t="n">
-        <v>403868</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>362199.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>362199.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5.820766091346741e-11</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>582704.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>582704.1000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>926266.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>926266.8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>136851.3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>136851.3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>645499.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>645499.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>695310.4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>695310.4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>413907.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>413907.6</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-5.820766091346741e-11</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>399334.9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>399334.9000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-5.820766091346741e-11</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>604805.7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>604805.7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>941299.9</v>
-      </c>
-      <c r="D26" t="n">
-        <v>941299.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>146658</v>
-      </c>
-      <c r="D27" t="n">
-        <v>146658</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>604228.4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>604228.4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>670365.5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>670365.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="G5" t="n">
+        <v>3780600</v>
       </c>
     </row>
   </sheetData>
@@ -21310,6 +20696,780 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>strategy_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>strategy_total</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>program_sum</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>296003.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>296003.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>396125.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>396125.5000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>549514</v>
+      </c>
+      <c r="D4" t="n">
+        <v>549514</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>759861.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>759861.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>122964.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>122964.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>658012.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>658012.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>402518</v>
+      </c>
+      <c r="D8" t="n">
+        <v>402518</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>386149.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>386149.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>392028.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>392028.6000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.164153218269348e-10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>561167.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>561167.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>836382.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>836382.4999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>131020.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>131020.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>608210.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>608210.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>565041.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>565041.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>403868</v>
+      </c>
+      <c r="D16" t="n">
+        <v>403868</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>362199.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>362199.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>582704.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>582704.1000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.164153218269348e-10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>926266.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>926266.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>136851.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>136851.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>645499.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>645499.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>695310.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>695310.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>413907.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>413907.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>399334.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>399334.9000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>604805.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>604805.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>941299.9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>941299.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>146658</v>
+      </c>
+      <c r="D27" t="n">
+        <v>146658</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>604228.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>604228.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>670365.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>670365.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/thailand/budget_layer_all_years.xlsx
+++ b/thailand/budget_layer_all_years.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:N302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,11 @@
           <t>strategy_name_source</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>countable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,6 +533,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,6 +594,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,6 +659,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,6 +724,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,6 +789,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,6 +854,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -888,6 +919,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -948,6 +984,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1008,6 +1049,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1068,6 +1114,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1128,6 +1179,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1188,6 +1244,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1248,6 +1309,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1308,6 +1374,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1368,6 +1439,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1410,6 +1486,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1470,6 +1547,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1530,6 +1612,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1590,6 +1677,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1650,6 +1742,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1710,6 +1807,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1770,6 +1872,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1830,6 +1937,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1890,6 +2002,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1950,6 +2067,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2010,6 +2132,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2070,6 +2197,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2130,6 +2262,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2190,6 +2327,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2250,6 +2392,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2310,6 +2457,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2352,6 +2504,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2412,6 +2565,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2472,6 +2630,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2532,6 +2695,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2592,6 +2760,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2652,6 +2825,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2712,6 +2890,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2772,6 +2955,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2832,6 +3020,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2874,6 +3067,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2934,6 +3128,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2994,6 +3193,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3054,6 +3258,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3114,6 +3323,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3174,6 +3388,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3234,6 +3453,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3294,6 +3518,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3354,6 +3583,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3414,6 +3648,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3474,6 +3713,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3534,6 +3778,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3576,6 +3825,7 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3636,6 +3886,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3696,6 +3951,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3756,6 +4016,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3816,6 +4081,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3876,6 +4146,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3936,6 +4211,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3996,6 +4276,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4056,6 +4341,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4116,6 +4406,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4158,6 +4453,7 @@
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4218,6 +4514,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4278,6 +4579,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4338,6 +4644,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4398,6 +4709,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4458,6 +4774,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4518,6 +4839,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4578,6 +4904,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4620,6 +4951,7 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4680,6 +5012,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4740,6 +5077,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4782,6 +5124,7 @@
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4842,6 +5185,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4902,6 +5250,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4962,6 +5315,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5022,6 +5380,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5082,6 +5445,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5142,6 +5510,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5202,6 +5575,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5262,6 +5640,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5322,6 +5705,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5382,6 +5770,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5442,6 +5835,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5502,6 +5900,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5562,6 +5965,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5604,6 +6012,7 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5664,6 +6073,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5724,6 +6138,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5784,6 +6203,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5844,6 +6268,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5904,6 +6333,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5964,6 +6398,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6024,6 +6463,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6084,6 +6528,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6144,6 +6593,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6204,6 +6658,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6264,6 +6723,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6324,6 +6788,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6384,6 +6853,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6444,6 +6918,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6504,6 +6983,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6564,6 +7048,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6606,6 +7095,7 @@
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6666,6 +7156,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6726,6 +7221,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6786,6 +7286,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6846,6 +7351,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6906,6 +7416,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6966,6 +7481,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7026,6 +7546,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7086,6 +7611,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7128,6 +7658,7 @@
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7188,6 +7719,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7248,6 +7784,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7308,6 +7849,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7368,6 +7914,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7428,6 +7979,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7488,6 +8044,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7548,6 +8109,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7608,6 +8174,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7668,6 +8239,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7728,6 +8304,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7788,6 +8369,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7830,6 +8416,7 @@
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7890,6 +8477,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7950,6 +8542,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8010,6 +8607,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8070,6 +8672,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8130,6 +8737,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8190,6 +8802,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8250,6 +8867,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8310,6 +8932,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8370,6 +8997,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8430,6 +9062,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8472,6 +9109,7 @@
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8532,6 +9170,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8592,6 +9235,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8652,6 +9300,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8712,6 +9365,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8772,6 +9430,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8832,6 +9495,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8892,6 +9560,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8934,6 +9607,7 @@
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8994,6 +9668,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9054,6 +9733,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9114,6 +9798,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9156,6 +9845,7 @@
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9216,6 +9906,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9276,6 +9971,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9336,6 +10036,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9396,6 +10101,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9456,6 +10166,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9516,6 +10231,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9576,6 +10296,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9636,6 +10361,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9696,6 +10426,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9756,6 +10491,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9816,6 +10556,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9876,6 +10621,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9936,6 +10686,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9978,6 +10733,7 @@
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10038,6 +10794,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10098,6 +10859,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10158,6 +10924,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10218,6 +10989,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10278,6 +11054,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10338,6 +11119,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10398,6 +11184,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10458,6 +11249,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10518,6 +11314,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10578,6 +11379,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10638,6 +11444,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10698,6 +11509,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10758,6 +11574,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10818,6 +11639,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10878,6 +11704,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10938,6 +11769,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10998,6 +11834,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11040,6 +11881,7 @@
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11100,6 +11942,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11160,6 +12007,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11220,6 +12072,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11280,6 +12137,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11340,6 +12202,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11400,6 +12267,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11460,6 +12332,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11520,6 +12397,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11562,6 +12444,7 @@
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11622,6 +12505,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11682,6 +12570,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11742,6 +12635,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11802,6 +12700,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11862,6 +12765,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11922,6 +12830,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11982,6 +12895,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12042,6 +12960,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12102,6 +13025,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12162,6 +13090,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12222,6 +13155,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12282,6 +13220,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12324,6 +13267,7 @@
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12384,6 +13328,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12444,6 +13393,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12504,6 +13458,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12564,6 +13523,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12624,6 +13588,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12684,6 +13653,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12744,6 +13718,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12804,6 +13783,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12864,6 +13848,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12924,6 +13913,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12966,6 +13960,7 @@
       </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13026,6 +14021,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13086,6 +14086,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13146,6 +14151,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13206,6 +14216,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13266,6 +14281,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13326,6 +14346,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13386,6 +14411,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13428,6 +14458,7 @@
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13488,6 +14519,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13548,6 +14584,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13590,6 +14631,7 @@
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13650,6 +14692,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13710,6 +14757,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13770,6 +14822,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13830,6 +14887,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13890,6 +14952,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13950,6 +15017,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14010,6 +15082,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14070,6 +15147,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14130,6 +15212,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14190,6 +15277,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14250,6 +15342,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14310,6 +15407,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14370,6 +15472,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14430,6 +15537,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14472,6 +15584,7 @@
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14532,6 +15645,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14592,6 +15710,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14652,6 +15775,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14712,6 +15840,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14772,6 +15905,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14832,6 +15970,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14892,6 +16035,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14952,6 +16100,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15012,6 +16165,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15072,6 +16230,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15132,6 +16295,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15192,6 +16360,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15252,6 +16425,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15312,6 +16490,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15372,6 +16555,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15432,6 +16620,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15474,6 +16667,7 @@
       </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15534,6 +16728,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15594,6 +16793,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15654,6 +16858,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15714,6 +16923,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15774,6 +16988,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15834,6 +17053,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15894,6 +17118,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15954,6 +17183,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15996,6 +17230,7 @@
       </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16056,6 +17291,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16116,6 +17356,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16176,6 +17421,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16236,6 +17486,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16296,6 +17551,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16356,6 +17616,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16416,6 +17681,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16476,6 +17746,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16536,6 +17811,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16596,6 +17876,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16656,6 +17941,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16716,6 +18006,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16758,6 +18053,7 @@
       </c>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16818,6 +18114,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16878,6 +18179,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16938,6 +18244,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16998,6 +18309,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17058,6 +18374,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17118,6 +18439,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17178,6 +18504,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17238,6 +18569,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17298,6 +18634,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17358,6 +18699,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17400,6 +18746,7 @@
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17460,6 +18807,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17520,6 +18872,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17580,6 +18937,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17640,6 +19002,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17700,6 +19067,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17760,6 +19132,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17820,6 +19197,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17862,6 +19244,7 @@
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17922,6 +19305,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17982,6 +19370,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18040,6 +19433,11 @@
       <c r="L302" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
